--- a/Data/First_part_GBD.xlsx
+++ b/Data/First_part_GBD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rayanaloliet/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gh13047/repo/GWAS-GBD/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171852E4-914A-304B-A1CB-01115816A22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165E658B-1976-1B40-A61A-000849A19964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="889">
   <si>
     <t>GBD term</t>
   </si>
@@ -2459,9 +2459,6 @@
     <t>Drug-susceptible tuberculosis</t>
   </si>
   <si>
-    <t>MONDO:0041806</t>
-  </si>
-  <si>
     <t>HIV/AIDS - Multidrug-resistant Tuberculosis without extensive drug resistance</t>
   </si>
   <si>
@@ -2667,6 +2664,30 @@
   </si>
   <si>
     <t>DOID:0080600</t>
+  </si>
+  <si>
+    <t>MONDO:0019640</t>
+  </si>
+  <si>
+    <t>EFO:0007918</t>
+  </si>
+  <si>
+    <t>MONDO:0006052</t>
+  </si>
+  <si>
+    <t>MONDO:0000368</t>
+  </si>
+  <si>
+    <t>EFO:0803635</t>
+  </si>
+  <si>
+    <t>MONDO:0044887</t>
+  </si>
+  <si>
+    <t>MONDO:0005089</t>
+  </si>
+  <si>
+    <t>MONDO:0006424</t>
   </si>
 </sst>
 </file>
@@ -5828,6 +5849,9 @@
       <c r="C197" t="s">
         <v>797</v>
       </c>
+      <c r="D197" t="s">
+        <v>881</v>
+      </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
@@ -5888,12 +5912,24 @@
         <v>811</v>
       </c>
       <c r="B204" t="s">
-        <v>812</v>
+        <v>175</v>
+      </c>
+      <c r="C204" t="s">
+        <v>882</v>
+      </c>
+      <c r="D204" t="s">
+        <v>883</v>
+      </c>
+      <c r="E204" t="s">
+        <v>884</v>
+      </c>
+      <c r="F204" t="s">
+        <v>885</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B205" t="s">
         <v>802</v>
@@ -5901,7 +5937,7 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B206" t="s">
         <v>802</v>
@@ -5909,18 +5945,18 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
+        <v>814</v>
+      </c>
+      <c r="B207" t="s">
         <v>815</v>
-      </c>
-      <c r="B207" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
+        <v>816</v>
+      </c>
+      <c r="B208" t="s">
         <v>817</v>
-      </c>
-      <c r="B208" t="s">
-        <v>818</v>
       </c>
       <c r="C208" t="s">
         <v>809</v>
@@ -5928,65 +5964,65 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
+        <v>818</v>
+      </c>
+      <c r="B209" t="s">
         <v>819</v>
-      </c>
-      <c r="B209" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
+        <v>820</v>
+      </c>
+      <c r="B210" t="s">
         <v>821</v>
       </c>
-      <c r="B210" t="s">
+      <c r="C210" t="s">
         <v>822</v>
-      </c>
-      <c r="C210" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
+        <v>823</v>
+      </c>
+      <c r="B211" t="s">
         <v>824</v>
-      </c>
-      <c r="B211" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
+        <v>825</v>
+      </c>
+      <c r="B212" t="s">
         <v>826</v>
       </c>
-      <c r="B212" t="s">
+      <c r="C212" t="s">
         <v>827</v>
-      </c>
-      <c r="C212" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
+        <v>828</v>
+      </c>
+      <c r="B213" t="s">
         <v>829</v>
       </c>
-      <c r="B213" t="s">
+      <c r="C213" t="s">
         <v>830</v>
       </c>
-      <c r="C213" t="s">
+      <c r="D213" t="s">
         <v>831</v>
-      </c>
-      <c r="D213" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
+        <v>832</v>
+      </c>
+      <c r="B214" t="s">
         <v>833</v>
       </c>
-      <c r="B214" t="s">
+      <c r="C214" t="s">
         <v>834</v>
-      </c>
-      <c r="C214" t="s">
-        <v>835</v>
       </c>
       <c r="D214" t="s">
         <v>55</v>
@@ -5994,162 +6030,171 @@
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
+        <v>835</v>
+      </c>
+      <c r="B215" t="s">
         <v>836</v>
       </c>
-      <c r="B215" t="s">
+      <c r="C215" t="s">
         <v>837</v>
       </c>
-      <c r="C215" t="s">
+      <c r="D215" t="s">
         <v>838</v>
       </c>
-      <c r="D215" t="s">
+      <c r="E215" t="s">
         <v>839</v>
       </c>
-      <c r="E215" t="s">
+      <c r="F215" t="s">
         <v>840</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>841</v>
-      </c>
-      <c r="G215" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
+        <v>842</v>
+      </c>
+      <c r="B216" t="s">
         <v>843</v>
       </c>
-      <c r="B216" t="s">
+      <c r="C216" t="s">
         <v>844</v>
-      </c>
-      <c r="C216" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
+        <v>845</v>
+      </c>
+      <c r="B217" t="s">
         <v>846</v>
       </c>
-      <c r="B217" t="s">
+      <c r="C217" t="s">
         <v>847</v>
       </c>
-      <c r="C217" t="s">
+      <c r="D217" t="s">
         <v>848</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
         <v>849</v>
-      </c>
-      <c r="E217" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
+        <v>850</v>
+      </c>
+      <c r="B218" t="s">
         <v>851</v>
       </c>
-      <c r="B218" t="s">
+      <c r="C218" t="s">
         <v>852</v>
       </c>
-      <c r="C218" t="s">
+      <c r="D218" t="s">
         <v>853</v>
-      </c>
-      <c r="D218" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
+        <v>854</v>
+      </c>
+      <c r="B219" t="s">
         <v>855</v>
       </c>
-      <c r="B219" t="s">
-        <v>856</v>
+      <c r="C219" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
+        <v>856</v>
+      </c>
+      <c r="B220" t="s">
         <v>857</v>
       </c>
-      <c r="B220" t="s">
+      <c r="C220" t="s">
         <v>858</v>
-      </c>
-      <c r="C220" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
+        <v>859</v>
+      </c>
+      <c r="B221" t="s">
         <v>860</v>
       </c>
-      <c r="B221" t="s">
+      <c r="C221" t="s">
         <v>861</v>
       </c>
-      <c r="C221" t="s">
+      <c r="D221" t="s">
         <v>862</v>
       </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
         <v>863</v>
-      </c>
-      <c r="E221" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
+        <v>864</v>
+      </c>
+      <c r="B222" t="s">
         <v>865</v>
       </c>
-      <c r="B222" t="s">
+      <c r="C222" t="s">
         <v>866</v>
       </c>
-      <c r="C222" t="s">
-        <v>867</v>
+      <c r="D222" t="s">
+        <v>887</v>
+      </c>
+      <c r="E222" t="s">
+        <v>888</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
+        <v>867</v>
+      </c>
+      <c r="B223" t="s">
         <v>868</v>
       </c>
-      <c r="B223" t="s">
+      <c r="C223" t="s">
         <v>869</v>
       </c>
-      <c r="C223" t="s">
+      <c r="D223" t="s">
         <v>870</v>
       </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
         <v>871</v>
-      </c>
-      <c r="E223" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
+        <v>872</v>
+      </c>
+      <c r="B224" t="s">
         <v>873</v>
       </c>
-      <c r="B224" t="s">
+      <c r="C224" t="s">
         <v>874</v>
       </c>
-      <c r="C224" t="s">
+      <c r="D224" t="s">
         <v>875</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>876</v>
       </c>
-      <c r="E224" t="s">
+      <c r="F224" t="s">
         <v>877</v>
-      </c>
-      <c r="F224" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
+        <v>878</v>
+      </c>
+      <c r="B225" t="s">
         <v>879</v>
       </c>
-      <c r="B225" t="s">
+      <c r="C225" t="s">
         <v>880</v>
-      </c>
-      <c r="C225" t="s">
-        <v>881</v>
       </c>
     </row>
   </sheetData>
